--- a/back_end/data/warehouse/에이스처인.xlsx
+++ b/back_end/data/warehouse/에이스처인.xlsx
@@ -16,7 +16,7 @@
     <t xml:space="preserve">현 재 고  현 황</t>
   </si>
   <si>
-    <t xml:space="preserve">위탁자 : 8189                                 조회일자 : 2026-05-29</t>
+    <t xml:space="preserve">위탁자 : 8189                                 조회일자 : 2026-06-05</t>
   </si>
   <si>
     <t>수탁품</t>
@@ -58,96 +58,66 @@
     <t>비고</t>
   </si>
   <si>
-    <t>NOLAN)우삼겹양지GFYG</t>
-  </si>
-  <si>
-    <t>26368398</t>
+    <t>EXCEL)우스지</t>
+  </si>
+  <si>
+    <t>26363732</t>
+  </si>
+  <si>
+    <t>평중/제니스</t>
+  </si>
+  <si>
+    <t>BOX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">250513-03334-5458655     -0202-00500</t>
+  </si>
+  <si>
+    <t>HDMUDALA33344700</t>
+  </si>
+  <si>
+    <t>803074900630</t>
+  </si>
+  <si>
+    <t>86R</t>
+  </si>
+  <si>
+    <t>A40301</t>
+  </si>
+  <si>
+    <t>통관</t>
+  </si>
+  <si>
+    <t>미국</t>
+  </si>
+  <si>
+    <t>26359806</t>
+  </si>
+  <si>
+    <t>평중/더베</t>
+  </si>
+  <si>
+    <t xml:space="preserve">250604-03334-9795358     -0102-00453</t>
+  </si>
+  <si>
+    <t>HDMUDALA45120900</t>
+  </si>
+  <si>
+    <t>803074900632</t>
+  </si>
+  <si>
+    <t>86E</t>
+  </si>
+  <si>
+    <t>A40201</t>
+  </si>
+  <si>
+    <t>26359859</t>
   </si>
   <si>
     <t>평중</t>
   </si>
   <si>
-    <t>BOX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">260227-00102-2026178     -0312-00026</t>
-  </si>
-  <si>
-    <t>COSU6443038520</t>
-  </si>
-  <si>
-    <t>801146400098</t>
-  </si>
-  <si>
-    <t>80</t>
-  </si>
-  <si>
-    <t>A30401</t>
-  </si>
-  <si>
-    <t>통관</t>
-  </si>
-  <si>
-    <t>호주</t>
-  </si>
-  <si>
-    <t>EXCEL)우스지</t>
-  </si>
-  <si>
-    <t>26359860</t>
-  </si>
-  <si>
-    <t xml:space="preserve">250513-03334-5458655     -0102-00809</t>
-  </si>
-  <si>
-    <t>HDMUDALA33344700</t>
-  </si>
-  <si>
-    <t>803074900630</t>
-  </si>
-  <si>
-    <t>86R</t>
-  </si>
-  <si>
-    <t>A40301</t>
-  </si>
-  <si>
-    <t>미국</t>
-  </si>
-  <si>
-    <t>26363732</t>
-  </si>
-  <si>
-    <t>평중/제니스</t>
-  </si>
-  <si>
-    <t xml:space="preserve">250513-03334-5458655     -0202-00500</t>
-  </si>
-  <si>
-    <t>26359806</t>
-  </si>
-  <si>
-    <t>평중/더베</t>
-  </si>
-  <si>
-    <t xml:space="preserve">250604-03334-9795358     -0102-00453</t>
-  </si>
-  <si>
-    <t>HDMUDALA45120900</t>
-  </si>
-  <si>
-    <t>803074900632</t>
-  </si>
-  <si>
-    <t>86E</t>
-  </si>
-  <si>
-    <t>A40201</t>
-  </si>
-  <si>
-    <t>26359859</t>
-  </si>
-  <si>
     <t xml:space="preserve">250604-03334-9795358     -0102-00809</t>
   </si>
   <si>
@@ -175,28 +145,13 @@
     <t>캐나다</t>
   </si>
   <si>
-    <t>SMITH/FL)돈목전지</t>
-  </si>
-  <si>
-    <t>26376243</t>
-  </si>
-  <si>
-    <t>평중/성원/고진/제이코</t>
-  </si>
-  <si>
-    <t xml:space="preserve">260508-01518-9500069     -0515-01518</t>
-  </si>
-  <si>
-    <t>NAM8403150</t>
-  </si>
-  <si>
-    <t>903058101088</t>
-  </si>
-  <si>
-    <t>717</t>
-  </si>
-  <si>
-    <t>A20302</t>
+    <t>26378304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">260513-00740-4088225     -0601-00100</t>
+  </si>
+  <si>
+    <t>A10301</t>
   </si>
   <si>
     <t>IBP)우척갈비CH CAB</t>
@@ -247,10 +202,10 @@
     <t xml:space="preserve">250508-03321-8740193     -0416-00562</t>
   </si>
   <si>
-    <t>3,192</t>
-  </si>
-  <si>
-    <t>27,233.02</t>
+    <t>2,917</t>
+  </si>
+  <si>
+    <t>25,354.60</t>
   </si>
 </sst>
 </file>
@@ -641,7 +596,7 @@
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="9.14" customWidth="1"/>
-    <col min="3" max="3" width="20.86" customWidth="1"/>
+    <col min="3" max="3" width="16.29" customWidth="1"/>
     <col min="4" max="4" width="5" customWidth="1"/>
     <col min="5" max="5" width="30.86" customWidth="1"/>
     <col min="6" max="6" width="19.14" customWidth="1"/>
@@ -653,7 +608,7 @@
     <col min="12" max="12" width="9.57" customWidth="1"/>
     <col min="13" max="13" width="5" customWidth="1"/>
     <col min="14" max="14" width="7" customWidth="1"/>
-    <col min="15" max="15" width="24.29" customWidth="1"/>
+    <col min="15" max="15" width="28.86" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
@@ -823,13 +778,13 @@
         <v>24</v>
       </c>
       <c r="J7" s="6">
-        <v>21</v>
+        <v>298</v>
       </c>
       <c r="K7" s="7">
-        <v>311.85000000000002</v>
+        <v>2026.4000000000001</v>
       </c>
       <c r="L7" s="8">
-        <v>46760</v>
+        <v>46392</v>
       </c>
       <c t="s" r="M7" s="5">
         <v>25</v>
@@ -840,13 +795,13 @@
     </row>
     <row r="8" ht="14.25" customHeight="1">
       <c t="s" r="A8" s="5">
+        <v>16</v>
+      </c>
+      <c t="s" r="B8" s="5">
         <v>27</v>
       </c>
-      <c t="s" r="B8" s="5">
+      <c t="s" r="C8" s="5">
         <v>28</v>
-      </c>
-      <c t="s" r="C8" s="5">
-        <v>18</v>
       </c>
       <c t="s" r="D8" s="5">
         <v>19</v>
@@ -867,36 +822,36 @@
         <v>33</v>
       </c>
       <c r="J8" s="6">
-        <v>52</v>
+        <v>358</v>
       </c>
       <c r="K8" s="7">
-        <v>353.60000000000002</v>
+        <v>2434.4000000000001</v>
       </c>
       <c r="L8" s="8">
-        <v>46392</v>
+        <v>46469</v>
       </c>
       <c t="s" r="M8" s="5">
         <v>25</v>
       </c>
       <c t="s" r="N8" s="5">
-        <v>34</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9" ht="14.25" customHeight="1">
       <c t="s" r="A9" s="5">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c t="s" r="B9" s="5">
+        <v>34</v>
+      </c>
+      <c t="s" r="C9" s="5">
         <v>35</v>
-      </c>
-      <c t="s" r="C9" s="5">
-        <v>36</v>
       </c>
       <c t="s" r="D9" s="5">
         <v>19</v>
       </c>
       <c t="s" r="E9" s="5">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c t="s" r="F9" s="5">
         <v>30</v>
@@ -911,74 +866,74 @@
         <v>33</v>
       </c>
       <c r="J9" s="6">
-        <v>350</v>
+        <v>809</v>
       </c>
       <c r="K9" s="7">
-        <v>2380</v>
+        <v>5501.1999999999998</v>
       </c>
       <c r="L9" s="8">
-        <v>46392</v>
+        <v>46469</v>
       </c>
       <c t="s" r="M9" s="5">
         <v>25</v>
       </c>
       <c t="s" r="N9" s="5">
-        <v>34</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" ht="14.25" customHeight="1">
       <c t="s" r="A10" s="5">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c t="s" r="B10" s="5">
         <v>38</v>
       </c>
       <c t="s" r="C10" s="5">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c t="s" r="D10" s="5">
         <v>19</v>
       </c>
       <c t="s" r="E10" s="5">
+        <v>39</v>
+      </c>
+      <c t="s" r="F10" s="5">
         <v>40</v>
       </c>
-      <c t="s" r="F10" s="5">
+      <c t="s" r="G10" s="5">
         <v>41</v>
       </c>
-      <c t="s" r="G10" s="5">
+      <c t="s" r="H10" s="5">
         <v>42</v>
       </c>
-      <c t="s" r="H10" s="5">
+      <c t="s" r="I10" s="5">
         <v>43</v>
       </c>
-      <c t="s" r="I10" s="5">
-        <v>44</v>
-      </c>
       <c r="J10" s="6">
-        <v>358</v>
+        <v>100</v>
       </c>
       <c r="K10" s="7">
-        <v>2434.4000000000001</v>
+        <v>2999</v>
       </c>
       <c r="L10" s="8">
-        <v>46469</v>
+        <v>46807</v>
       </c>
       <c t="s" r="M10" s="5">
         <v>25</v>
       </c>
       <c t="s" r="N10" s="5">
-        <v>34</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" ht="14.25" customHeight="1">
       <c t="s" r="A11" s="5">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c t="s" r="B11" s="5">
         <v>45</v>
       </c>
       <c t="s" r="C11" s="5">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c t="s" r="D11" s="5">
         <v>19</v>
@@ -987,272 +942,184 @@
         <v>46</v>
       </c>
       <c t="s" r="F11" s="5">
+        <v>40</v>
+      </c>
+      <c t="s" r="G11" s="5">
         <v>41</v>
       </c>
-      <c t="s" r="G11" s="5">
+      <c t="s" r="H11" s="5">
         <v>42</v>
       </c>
-      <c t="s" r="H11" s="5">
-        <v>43</v>
-      </c>
       <c t="s" r="I11" s="5">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="J11" s="6">
-        <v>809</v>
+        <v>100</v>
       </c>
       <c r="K11" s="7">
-        <v>5501.1999999999998</v>
+        <v>2999</v>
       </c>
       <c r="L11" s="8">
-        <v>46469</v>
+        <v>46807</v>
       </c>
       <c t="s" r="M11" s="5">
         <v>25</v>
       </c>
       <c t="s" r="N11" s="5">
-        <v>34</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12" ht="14.25" customHeight="1">
       <c t="s" r="A12" s="5">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c t="s" r="B12" s="5">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c t="s" r="C12" s="5">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c t="s" r="D12" s="5">
         <v>19</v>
       </c>
       <c t="s" r="E12" s="5">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c t="s" r="F12" s="5">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c t="s" r="G12" s="5">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c t="s" r="H12" s="5">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c t="s" r="I12" s="5">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="J12" s="6">
-        <v>100</v>
+        <v>44</v>
       </c>
       <c r="K12" s="7">
-        <v>2999</v>
+        <v>1180.2</v>
       </c>
       <c r="L12" s="8">
-        <v>46807</v>
+        <v>46612</v>
       </c>
       <c t="s" r="M12" s="5">
         <v>25</v>
       </c>
       <c t="s" r="N12" s="5">
-        <v>54</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13" ht="14.25" customHeight="1">
       <c t="s" r="A13" s="5">
-        <v>55</v>
+        <v>16</v>
       </c>
       <c t="s" r="B13" s="5">
         <v>56</v>
       </c>
       <c t="s" r="C13" s="5">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c t="s" r="D13" s="5">
         <v>19</v>
       </c>
       <c t="s" r="E13" s="5">
+        <v>57</v>
+      </c>
+      <c t="s" r="F13" s="5">
         <v>58</v>
       </c>
-      <c t="s" r="F13" s="5">
+      <c t="s" r="G13" s="5">
         <v>59</v>
       </c>
-      <c t="s" r="G13" s="5">
+      <c t="s" r="H13" s="5">
         <v>60</v>
       </c>
-      <c t="s" r="H13" s="5">
+      <c t="s" r="I13" s="5">
         <v>61</v>
       </c>
-      <c t="s" r="I13" s="5">
-        <v>62</v>
-      </c>
       <c r="J13" s="6">
-        <v>250</v>
+        <v>646</v>
       </c>
       <c r="K13" s="7">
-        <v>3858.3699999999999</v>
+        <v>4392.8000000000002</v>
       </c>
       <c r="L13" s="8">
-        <v>46759</v>
+        <v>46450</v>
       </c>
       <c t="s" r="M13" s="5">
         <v>25</v>
       </c>
       <c t="s" r="N13" s="5">
-        <v>34</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14" ht="14.25" customHeight="1">
       <c t="s" r="A14" s="5">
-        <v>63</v>
+        <v>16</v>
       </c>
       <c t="s" r="B14" s="5">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c t="s" r="C14" s="5">
-        <v>65</v>
+        <v>35</v>
       </c>
       <c t="s" r="D14" s="5">
         <v>19</v>
       </c>
       <c t="s" r="E14" s="5">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c t="s" r="F14" s="5">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c t="s" r="G14" s="5">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c t="s" r="H14" s="5">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c t="s" r="I14" s="5">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="J14" s="6">
-        <v>44</v>
+        <v>562</v>
       </c>
       <c r="K14" s="7">
-        <v>1180.2</v>
+        <v>3821.5999999999999</v>
       </c>
       <c r="L14" s="8">
-        <v>46612</v>
+        <v>46450</v>
       </c>
       <c t="s" r="M14" s="5">
         <v>25</v>
       </c>
       <c t="s" r="N14" s="5">
-        <v>34</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" ht="14.25" customHeight="1">
-      <c t="s" r="A15" s="5">
-        <v>27</v>
-      </c>
-      <c t="s" r="B15" s="5">
-        <v>71</v>
-      </c>
-      <c t="s" r="C15" s="5">
-        <v>39</v>
-      </c>
-      <c t="s" r="D15" s="5">
-        <v>19</v>
-      </c>
-      <c t="s" r="E15" s="5">
-        <v>72</v>
-      </c>
-      <c t="s" r="F15" s="5">
-        <v>73</v>
-      </c>
-      <c t="s" r="G15" s="5">
-        <v>74</v>
-      </c>
-      <c t="s" r="H15" s="5">
-        <v>75</v>
-      </c>
-      <c t="s" r="I15" s="5">
-        <v>76</v>
-      </c>
-      <c r="J15" s="6">
-        <v>646</v>
-      </c>
-      <c r="K15" s="7">
-        <v>4392.8000000000002</v>
-      </c>
-      <c r="L15" s="8">
-        <v>46450</v>
-      </c>
-      <c t="s" r="M15" s="5">
-        <v>25</v>
-      </c>
-      <c t="s" r="N15" s="5">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="16" ht="14.25" customHeight="1">
-      <c t="s" r="A16" s="5">
-        <v>27</v>
-      </c>
-      <c t="s" r="B16" s="5">
-        <v>77</v>
-      </c>
-      <c t="s" r="C16" s="5">
-        <v>18</v>
-      </c>
-      <c t="s" r="D16" s="5">
-        <v>19</v>
-      </c>
-      <c t="s" r="E16" s="5">
-        <v>78</v>
-      </c>
-      <c t="s" r="F16" s="5">
-        <v>73</v>
-      </c>
-      <c t="s" r="G16" s="5">
-        <v>74</v>
-      </c>
-      <c t="s" r="H16" s="5">
-        <v>75</v>
-      </c>
-      <c t="s" r="I16" s="5">
-        <v>76</v>
-      </c>
-      <c r="J16" s="6">
-        <v>562</v>
-      </c>
-      <c r="K16" s="7">
-        <v>3821.5999999999999</v>
-      </c>
-      <c r="L16" s="8">
-        <v>46450</v>
-      </c>
-      <c t="s" r="M16" s="5">
-        <v>25</v>
-      </c>
-      <c t="s" r="N16" s="5">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="17" ht="14.25" customHeight="1">
-      <c r="A17" s="9"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="9"/>
-      <c t="s" r="J17" s="10">
-        <v>79</v>
-      </c>
-      <c t="s" r="K17" s="10">
-        <v>80</v>
-      </c>
-      <c r="L17" s="9"/>
-      <c r="M17" s="9"/>
-      <c r="N17" s="9"/>
+      <c r="A15" s="9"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="9"/>
+      <c r="G15" s="9"/>
+      <c r="H15" s="9"/>
+      <c r="I15" s="9"/>
+      <c t="s" r="J15" s="10">
+        <v>64</v>
+      </c>
+      <c t="s" r="K15" s="10">
+        <v>65</v>
+      </c>
+      <c r="L15" s="9"/>
+      <c r="M15" s="9"/>
+      <c r="N15" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="17">
